--- a/Anexo_07_Diferencias_por_familia/Anexo_07_Diferencias_por_familia.xlsx
+++ b/Anexo_07_Diferencias_por_familia/Anexo_07_Diferencias_por_familia.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1299105378781284</v>
+        <v>0.1357406916656771</v>
       </c>
       <c r="C2" t="n">
         <v>0.1320016853597622</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0020911474816337</v>
+        <v>0.0037390063059149</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0020911474816337</v>
+        <v>0.0037390063059149</v>
       </c>
     </row>
     <row r="3">
@@ -474,16 +474,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0769866119295803</v>
+        <v>0.07612159381801201</v>
       </c>
       <c r="C3" t="n">
         <v>0.0733858865615291</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0036007253680511</v>
+        <v>0.0027357072564828</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0036007253680511</v>
+        <v>0.0027357072564828</v>
       </c>
     </row>
     <row r="4">
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0630979789722394</v>
+        <v>0.0623890129163716</v>
       </c>
       <c r="C4" t="n">
         <v>0.0611200394751261</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0019779394971133</v>
+        <v>0.0012689734412454</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0019779394971133</v>
+        <v>0.0012689734412454</v>
       </c>
     </row>
     <row r="5">
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0563508113475682</v>
+        <v>0.0557424195809022</v>
       </c>
       <c r="C5" t="n">
         <v>0.0432711259374991</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0130796854100691</v>
+        <v>0.0124712936434031</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0130796854100691</v>
+        <v>0.0124712936434031</v>
       </c>
     </row>
     <row r="6">
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.048292803095944</v>
+        <v>0.0482548893537844</v>
       </c>
       <c r="C6" t="n">
         <v>0.0415939754497899</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0066988276461541</v>
+        <v>0.0066609139039944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0066988276461541</v>
+        <v>0.0066609139039944</v>
       </c>
     </row>
     <row r="7">
@@ -550,16 +550,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0463996805809161</v>
+        <v>0.046643929680113</v>
       </c>
       <c r="C7" t="n">
         <v>0.043681190616139</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0027184899647771</v>
+        <v>0.002962739063974</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0027184899647771</v>
+        <v>0.002962739063974</v>
       </c>
     </row>
     <row r="8">
@@ -569,16 +569,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0444092736539337</v>
+        <v>0.0440494398704873</v>
       </c>
       <c r="C8" t="n">
         <v>0.0418586956401034</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0025505780138302</v>
+        <v>0.0021907442303838</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0025505780138302</v>
+        <v>0.0021907442303838</v>
       </c>
     </row>
     <row r="9">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0421700057523446</v>
+        <v>0.041725665721343</v>
       </c>
       <c r="C9" t="n">
         <v>0.0470687185340542</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0048987127817096</v>
+        <v>-0.0053430528127112</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0048987127817096</v>
+        <v>0.0053430528127112</v>
       </c>
     </row>
     <row r="10">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0316407544393511</v>
+        <v>0.0314750932083824</v>
       </c>
       <c r="C10" t="n">
         <v>0.0337561234099783</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0021153689706272</v>
+        <v>-0.0022810302015959</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0021153689706272</v>
+        <v>0.0022810302015959</v>
       </c>
     </row>
     <row r="11">
@@ -626,16 +626,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0293978859304383</v>
+        <v>0.0294945381020379</v>
       </c>
       <c r="C11" t="n">
         <v>0.0289038390069082</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0004940469235301</v>
+        <v>0.0005906990951297</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0004940469235301</v>
+        <v>0.0005906990951297</v>
       </c>
     </row>
     <row r="12">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0252943419525299</v>
+        <v>0.0250407953318603</v>
       </c>
       <c r="C12" t="n">
         <v>0.0261882323559152</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0008938904033852</v>
+        <v>-0.0011474370240548</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0008938904033852</v>
+        <v>0.0011474370240548</v>
       </c>
     </row>
     <row r="13">
@@ -664,16 +664,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0245030490580692</v>
+        <v>0.0242277339001133</v>
       </c>
       <c r="C13" t="n">
         <v>0.0199221355933919</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0045809134646772</v>
+        <v>0.0043055983067214</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0045809134646772</v>
+        <v>0.0043055983067214</v>
       </c>
     </row>
     <row r="14">
@@ -683,16 +683,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0203435841249636</v>
+        <v>0.0201150045280539</v>
       </c>
       <c r="C14" t="n">
         <v>0.0161101068644112</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0042334772605523</v>
+        <v>0.0040048976636426</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0042334772605523</v>
+        <v>0.0040048976636426</v>
       </c>
     </row>
     <row r="15">
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0187449163673487</v>
+        <v>0.0185342993295133</v>
       </c>
       <c r="C15" t="n">
         <v>0.0171578541758967</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0015870621914519</v>
+        <v>0.0013764451536166</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0015870621914519</v>
+        <v>0.0013764451536166</v>
       </c>
     </row>
     <row r="16">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0148159891143989</v>
+        <v>0.0146495173265967</v>
       </c>
       <c r="C16" t="n">
         <v>0.0136591634382695</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0011568256761294</v>
+        <v>0.0009903538883271001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0011568256761294</v>
+        <v>0.0009903538883271001</v>
       </c>
     </row>
     <row r="17">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0133779480774455</v>
+        <v>0.0132276340541034</v>
       </c>
       <c r="C17" t="n">
         <v>0.0100861349518567</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0032918131255887</v>
+        <v>0.0031414991022466</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0032918131255887</v>
+        <v>0.0031414991022466</v>
       </c>
     </row>
     <row r="18">
@@ -759,16 +759,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0128614297144717</v>
+        <v>0.012959836597051</v>
       </c>
       <c r="C18" t="n">
         <v>0.008156840110881801</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0047045896035899</v>
+        <v>0.0048029964861692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0047045896035899</v>
+        <v>0.0048029964861692</v>
       </c>
     </row>
     <row r="19">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0125744057254165</v>
+        <v>0.0128187527357559</v>
       </c>
       <c r="C19" t="n">
         <v>0.0102826619987523</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0022917437266642</v>
+        <v>0.0025360907370035</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0022917437266642</v>
+        <v>0.0025360907370035</v>
       </c>
     </row>
     <row r="20">
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0120342700621</v>
+        <v>0.0119497595889115</v>
       </c>
       <c r="C20" t="n">
         <v>0.008880379614286201</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0031538904478138</v>
+        <v>0.0030693799746252</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0031538904478138</v>
+        <v>0.0030693799746252</v>
       </c>
     </row>
     <row r="21">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.011280802383035</v>
+        <v>0.0111540517944616</v>
       </c>
       <c r="C21" t="n">
         <v>0.0101778342874389</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0011029680955961</v>
+        <v>0.0009762175070227</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0011029680955961</v>
+        <v>0.0009762175070227</v>
       </c>
     </row>
     <row r="22">
@@ -835,16 +835,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0110885346414809</v>
+        <v>0.0109639443646103</v>
       </c>
       <c r="C22" t="n">
         <v>0.013826991848362</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.002738457206881</v>
+        <v>-0.0028630474837516</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002738457206881</v>
+        <v>0.0028630474837516</v>
       </c>
     </row>
     <row r="23">
@@ -854,16 +854,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0109715210409555</v>
+        <v>0.0108482455236414</v>
       </c>
       <c r="C23" t="n">
         <v>0.0041611964581518</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0068103245828036</v>
+        <v>0.0066870490654895</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0068103245828036</v>
+        <v>0.0066870490654895</v>
       </c>
     </row>
     <row r="24">
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0107353950176529</v>
+        <v>0.0106147726017242</v>
       </c>
       <c r="C24" t="n">
         <v>0.0091846940477141</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0015507009699387</v>
+        <v>0.0014300785540101</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0015507009699387</v>
+        <v>0.0014300785540101</v>
       </c>
     </row>
     <row r="25">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0105273740850801</v>
+        <v>0.0104090889830006</v>
       </c>
       <c r="C25" t="n">
         <v>0.0094571875719947</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0010701865130853</v>
+        <v>0.0009519014110058</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0010701865130853</v>
+        <v>0.0009519014110058</v>
       </c>
     </row>
     <row r="26">
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0102396429893756</v>
+        <v>0.0101245908209557</v>
       </c>
       <c r="C26" t="n">
         <v>0.0120720219665116</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.001832378977136</v>
+        <v>-0.0019474311455559</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001832378977136</v>
+        <v>0.0019474311455559</v>
       </c>
     </row>
     <row r="27">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0098792917695226</v>
+        <v>0.009768288491213299</v>
       </c>
       <c r="C27" t="n">
         <v>0.0139518600442782</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0040725682747556</v>
+        <v>-0.0041835715530649</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0040725682747556</v>
+        <v>0.0041835715530649</v>
       </c>
     </row>
     <row r="28">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0091729103632391</v>
+        <v>0.009095786582011999</v>
       </c>
       <c r="C28" t="n">
         <v>0.008489895846277001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0006830145169621</v>
+        <v>0.000605890735735</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0006830145169621</v>
+        <v>0.000605890735735</v>
       </c>
     </row>
     <row r="29">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0090917765113548</v>
+        <v>0.0089896217190924</v>
       </c>
       <c r="C29" t="n">
         <v>0.0092162481130223</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0001244716016674</v>
+        <v>-0.0002266263939298</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0001244716016674</v>
+        <v>0.0002266263939298</v>
       </c>
     </row>
     <row r="30">
@@ -987,16 +987,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0088812816696955</v>
+        <v>0.0087814919880136</v>
       </c>
       <c r="C30" t="n">
         <v>0.0092040045022234</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0003227228325279</v>
+        <v>-0.0004225125142098</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0003227228325279</v>
+        <v>0.0004225125142098</v>
       </c>
     </row>
     <row r="31">
@@ -1006,16 +1006,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0085480083207813</v>
+        <v>0.008451963283469199</v>
       </c>
       <c r="C31" t="n">
         <v>0.0054723353009831</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0030756730197982</v>
+        <v>0.0029796279824861</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0030756730197982</v>
+        <v>0.0029796279824861</v>
       </c>
     </row>
     <row r="32">
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0081390210446476</v>
+        <v>0.0080475713699886</v>
       </c>
       <c r="C32" t="n">
         <v>0.0088998072428255</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0007607861981779</v>
+        <v>-0.0008522358728368</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0007607861981779</v>
+        <v>0.0008522358728368</v>
       </c>
     </row>
     <row r="33">
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.007277389688168</v>
+        <v>0.0071956212647055</v>
       </c>
       <c r="C33" t="n">
         <v>0.0092982268131773</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0020208371250092</v>
+        <v>-0.0021026055484718</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0020208371250092</v>
+        <v>0.0021026055484718</v>
       </c>
     </row>
     <row r="34">
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0067302737305604</v>
+        <v>0.0066676239910823</v>
       </c>
       <c r="C34" t="n">
         <v>0.0050177219848053</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0017125517457551</v>
+        <v>0.001649902006277</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0017125517457551</v>
+        <v>0.001649902006277</v>
       </c>
     </row>
     <row r="35">
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0064333915502903</v>
+        <v>0.0063611062519725</v>
       </c>
       <c r="C35" t="n">
         <v>0.0041620328391269</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0022713587111634</v>
+        <v>0.0021990734128455</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0022713587111634</v>
+        <v>0.0021990734128455</v>
       </c>
     </row>
     <row r="36">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0060182924450691</v>
+        <v>0.0059506711816414</v>
       </c>
       <c r="C36" t="n">
         <v>0.0066043138246934</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0005860213796242</v>
+        <v>-0.0006536426430519</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0005860213796242</v>
+        <v>0.0006536426430519</v>
       </c>
     </row>
     <row r="37">
@@ -1120,54 +1120,54 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0059467469808942</v>
+        <v>0.0058799295990864</v>
       </c>
       <c r="C37" t="n">
         <v>0.0069662762028716</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0010195292219774</v>
+        <v>-0.0010863466037852</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0010195292219774</v>
+        <v>0.0010863466037852</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Acidimicrobiaceae</t>
+          <t>Burkholderiaceae</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0056665323754516</v>
+        <v>0.0056807926422559</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0063526852875441</v>
+        <v>0.0046431273557335</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0006861529120924</v>
+        <v>0.0010376652865224</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0006861529120924</v>
+        <v>0.0010376652865224</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Burkholderiaceae</t>
+          <t>Acidimicrobiaceae</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0056371252134465</v>
+        <v>0.0056028634723567</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0046431273557335</v>
+        <v>0.0063526852875441</v>
       </c>
       <c r="D39" t="n">
-        <v>0.000993997857713</v>
+        <v>-0.0007498218151874</v>
       </c>
       <c r="E39" t="n">
-        <v>0.000993997857713</v>
+        <v>0.0007498218151874</v>
       </c>
     </row>
     <row r="40">
@@ -1177,16 +1177,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0053042837107639</v>
+        <v>0.0052446850173845</v>
       </c>
       <c r="C40" t="n">
         <v>0.0028503603504528</v>
       </c>
       <c r="D40" t="n">
-        <v>0.002453923360311</v>
+        <v>0.0023943246669317</v>
       </c>
       <c r="E40" t="n">
-        <v>0.002453923360311</v>
+        <v>0.0023943246669317</v>
       </c>
     </row>
     <row r="41">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.004559114401539</v>
+        <v>0.0045078883970273</v>
       </c>
       <c r="C41" t="n">
         <v>0.0049456867457959</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0003865723442569</v>
+        <v>-0.0004377983487686</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0003865723442569</v>
+        <v>0.0004377983487686</v>
       </c>
     </row>
     <row r="42">
@@ -1215,16 +1215,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0045405340229014</v>
+        <v>0.0044895167866891</v>
       </c>
       <c r="C42" t="n">
         <v>0.0038904904759181</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0006500435469833</v>
+        <v>0.0005990263107709</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0006500435469833</v>
+        <v>0.0005990263107709</v>
       </c>
     </row>
     <row r="43">
@@ -1234,16 +1234,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0045318096221571</v>
+        <v>0.0044808904129194</v>
       </c>
       <c r="C43" t="n">
         <v>0.0037712196629387</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0007605899592184</v>
+        <v>0.0007096707499806</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0007605899592184</v>
+        <v>0.0007096707499806</v>
       </c>
     </row>
     <row r="44">
@@ -1253,16 +1253,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0043306677470799</v>
+        <v>0.0042820085589105</v>
       </c>
       <c r="C44" t="n">
         <v>0.0048930736087346</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0005624058616547</v>
+        <v>-0.0006110650498241</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0005624058616547</v>
+        <v>0.0006110650498241</v>
       </c>
     </row>
     <row r="45">
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0038769414787302</v>
+        <v>0.0038333803385197</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006456073215225</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0032313341572076</v>
+        <v>0.0031877730169972</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0032313341572076</v>
+        <v>0.0031877730169972</v>
       </c>
     </row>
     <row r="46">
@@ -1291,16 +1291,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0035113197543831</v>
+        <v>0.003664078007891</v>
       </c>
       <c r="C46" t="n">
         <v>0.0027109352358633</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0008003845185197</v>
+        <v>0.0009531427720276</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0008003845185197</v>
+        <v>0.0009531427720276</v>
       </c>
     </row>
     <row r="47">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0034916163555092</v>
+        <v>0.0034523847110653</v>
       </c>
       <c r="C47" t="n">
         <v>0.0044890312420167</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0009974148865075001</v>
+        <v>-0.0010366465309514</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0009974148865075001</v>
+        <v>0.0010366465309514</v>
       </c>
     </row>
     <row r="48">
@@ -1329,16 +1329,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0034820122100383</v>
+        <v>0.0034428884773413</v>
       </c>
       <c r="C48" t="n">
         <v>0.0039495796292846</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0004675674192462</v>
+        <v>-0.0005066911519433</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0004675674192462</v>
+        <v>0.0005066911519433</v>
       </c>
     </row>
     <row r="49">
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0033467386565893</v>
+        <v>0.003309134851459</v>
       </c>
       <c r="C49" t="n">
         <v>0.0049863304576611</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.0016395918010718</v>
+        <v>-0.001677195606202</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0016395918010718</v>
+        <v>0.001677195606202</v>
       </c>
     </row>
     <row r="50">
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0029587042158305</v>
+        <v>0.0029254603482369</v>
       </c>
       <c r="C50" t="n">
         <v>0.002722069095898</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0002366351199325</v>
+        <v>0.0002033912523389</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0002366351199325</v>
+        <v>0.0002033912523389</v>
       </c>
     </row>
     <row r="51">
@@ -1386,16 +1386,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0028569716161367</v>
+        <v>0.002824870811461</v>
       </c>
       <c r="C51" t="n">
         <v>0.0019769350164158</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0008800365997208</v>
+        <v>0.0008479357950451</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0008800365997208</v>
+        <v>0.0008479357950451</v>
       </c>
     </row>
     <row r="52">
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0026089045229007</v>
+        <v>0.0028189706867434</v>
       </c>
       <c r="C52" t="n">
         <v>0.0054107834466091</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.0028018789237083</v>
+        <v>-0.0025918127598657</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0028018789237083</v>
+        <v>0.0025918127598657</v>
       </c>
     </row>
     <row r="53">
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0025580786198289</v>
+        <v>0.0025293361634263</v>
       </c>
       <c r="C53" t="n">
         <v>0.0030870896731382</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0005290110533092</v>
+        <v>-0.0005577535097118</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0005290110533092</v>
+        <v>0.0005577535097118</v>
       </c>
     </row>
     <row r="54">
@@ -1443,149 +1443,149 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0024365695541465</v>
+        <v>0.0024091923681448</v>
       </c>
       <c r="C54" t="n">
         <v>0.0011364467673831</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0013001227867633</v>
+        <v>0.0012727456007617</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0013001227867633</v>
+        <v>0.0012727456007617</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Legionellaceae</t>
+          <t>Bacteriovoracaceae</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0023946088044628</v>
+        <v>0.0023924139680609</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0008526346541119</v>
+        <v>0.0025554154931221</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0015419741503508</v>
+        <v>-0.0001630015250611</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0015419741503508</v>
+        <v>0.0001630015250611</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Phyllobacteriaceae</t>
+          <t>Legionellaceae</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0023701139001887</v>
+        <v>0.0023677030875587</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0008812496898922</v>
+        <v>0.0008526346541119</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0014888642102964</v>
+        <v>0.0015150684334468</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0014888642102964</v>
+        <v>0.0015150684334468</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Acidothermaceae</t>
+          <t>Phyllobacteriaceae</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0023478724902962</v>
+        <v>0.0023434834069282</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0001276362976928</v>
+        <v>0.0008812496898922</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0022202361926033</v>
+        <v>0.0014622337170359</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0022202361926033</v>
+        <v>0.0014622337170359</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nocardioidaceae</t>
+          <t>Acidothermaceae</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0023451411751223</v>
+        <v>0.0023214919005176</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0038846581763547</v>
+        <v>0.0001276362976928</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.0015395170012324</v>
+        <v>0.0021938556028247</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0015395170012324</v>
+        <v>0.0021938556028247</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Bacteriovoracaceae</t>
+          <t>Nocardioidaceae</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0022824502188762</v>
+        <v>0.0023187912742782</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0025554154931221</v>
+        <v>0.0038846581763547</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.0002729652742459</v>
+        <v>-0.0015658669020765</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0002729652742459</v>
+        <v>0.0015658669020765</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Thermoguttaceae</t>
+          <t>Micrococcaceae</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0022765892577884</v>
+        <v>0.0022982502060549</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0007409512603156</v>
+        <v>0.0008545021809634</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0015356379974728</v>
+        <v>0.0014437480250915</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0015356379974728</v>
+        <v>0.0014437480250915</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Micrococcaceae</t>
+          <t>Thermoguttaceae</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0022635435526448</v>
+        <v>0.0022510096032066</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0008545021809634</v>
+        <v>0.0007409512603156</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0014090413716814</v>
+        <v>0.0015100583428909</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0014090413716814</v>
+        <v>0.0015100583428909</v>
       </c>
     </row>
     <row r="62">
@@ -1595,16 +1595,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0020093213506772</v>
+        <v>0.0019867447062876</v>
       </c>
       <c r="C62" t="n">
         <v>0.0007932296240661</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0012160917266111</v>
+        <v>0.0011935150822214</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0012160917266111</v>
+        <v>0.0011935150822214</v>
       </c>
     </row>
     <row r="63">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0019732318337118</v>
+        <v>0.0019758241065274</v>
       </c>
       <c r="C63" t="n">
         <v>0.00142187808052</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0005513537531918</v>
+        <v>0.0005539460260073</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0005513537531918</v>
+        <v>0.0005539460260073</v>
       </c>
     </row>
     <row r="64">
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0019544078609277</v>
+        <v>0.0019324482220409</v>
       </c>
       <c r="C64" t="n">
         <v>0.000973603405836</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0009808044550917001</v>
+        <v>0.0009588448162048</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0009808044550917001</v>
+        <v>0.0009588448162048</v>
       </c>
     </row>
     <row r="65">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0019255074832216</v>
+        <v>0.0019038725676798</v>
       </c>
       <c r="C65" t="n">
         <v>0.0025231223003925</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0005976148171709</v>
+        <v>-0.0006192497327127</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0005976148171709</v>
+        <v>0.0006192497327127</v>
       </c>
     </row>
     <row r="66">
@@ -1671,111 +1671,111 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0019182126562554</v>
+        <v>0.0018966597050615</v>
       </c>
       <c r="C66" t="n">
         <v>0.0033154743522965</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.001397261696041</v>
+        <v>-0.0014188146472349</v>
       </c>
       <c r="E66" t="n">
-        <v>0.001397261696041</v>
+        <v>0.0014188146472349</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Labilitrichaceae</t>
+          <t>Flavobacteriaceae</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0018397378993107</v>
+        <v>0.0018255378828432</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0030714678933359</v>
+        <v>0.0012862053411499</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.0012317299940251</v>
+        <v>0.0005393325416932</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0012317299940251</v>
+        <v>0.0005393325416932</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Patulibacteraceae</t>
+          <t>Labilitrichaceae</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0018054029446984</v>
+        <v>0.0018190666869589</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0026199425995024</v>
+        <v>0.0030714678933359</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.000814539654804</v>
+        <v>-0.001252401206377</v>
       </c>
       <c r="E68" t="n">
-        <v>0.000814539654804</v>
+        <v>0.001252401206377</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sterolibacteriaceae</t>
+          <t>Patulibacteraceae</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.001735014573986</v>
+        <v>0.0017851175183535</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0007352092010856</v>
+        <v>0.0026199425995024</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0009998053729002999</v>
+        <v>-0.0008348250811489</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0009998053729002999</v>
+        <v>0.0008348250811489</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hymenobacteraceae</t>
+          <t>Sterolibacteriaceae</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0016974852754474</v>
+        <v>0.0017155200282109</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0017767211351043</v>
+        <v>0.0007352092010856</v>
       </c>
       <c r="D70" t="n">
-        <v>-7.923585965688299e-05</v>
+        <v>0.0009803108271252</v>
       </c>
       <c r="E70" t="n">
-        <v>7.923585965688299e-05</v>
+        <v>0.0009803108271252</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Flavobacteriaceae</t>
+          <t>Hymenobacteraceae</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0016339979711523</v>
+        <v>0.001678412407184</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0012862053411499</v>
+        <v>0.0017767211351043</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0003477926300023</v>
+        <v>-9.83087279203378e-05</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0003477926300023</v>
+        <v>9.83087279203378e-05</v>
       </c>
     </row>
     <row r="72">
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0016290813438156</v>
+        <v>0.0016402573174042</v>
       </c>
       <c r="C72" t="n">
         <v>0.0018312410587742</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.0002021597149585</v>
+        <v>-0.00019098374137</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0002021597149585</v>
+        <v>0.00019098374137</v>
       </c>
     </row>
     <row r="73">
@@ -1804,16 +1804,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.001598279359558</v>
+        <v>0.0016204143158636</v>
       </c>
       <c r="C73" t="n">
         <v>0.0029101456836378</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0013118663240798</v>
+        <v>-0.0012897313677741</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0013118663240798</v>
+        <v>0.0012897313677741</v>
       </c>
     </row>
     <row r="74">
@@ -1823,16 +1823,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0014255401287075</v>
+        <v>0.0014095228238905</v>
       </c>
       <c r="C74" t="n">
         <v>0.0007620968311767</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0006634432975307001</v>
+        <v>0.0006474259927138</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0006634432975307001</v>
+        <v>0.0006474259927138</v>
       </c>
     </row>
     <row r="75">
@@ -1842,16 +1842,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.001339643923523</v>
+        <v>0.001324591744607</v>
       </c>
       <c r="C75" t="n">
         <v>0.0022904173040824</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.0009507733805594</v>
+        <v>-0.0009658255594754001</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0009507733805594</v>
+        <v>0.0009658255594754001</v>
       </c>
     </row>
     <row r="76">
@@ -1861,16 +1861,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0012753110831914</v>
+        <v>0.0012869243725266</v>
       </c>
       <c r="C76" t="n">
         <v>0.0008867097162629</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0003886013669284</v>
+        <v>0.0004002146562636</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0003886013669284</v>
+        <v>0.0004002146562636</v>
       </c>
     </row>
     <row r="77">
@@ -1880,16 +1880,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0012581208588973</v>
+        <v>0.0012439846694715</v>
       </c>
       <c r="C77" t="n">
         <v>0.0016028942573592</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.0003447733984618</v>
+        <v>-0.0003589095878876</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0003447733984618</v>
+        <v>0.0003589095878876</v>
       </c>
     </row>
     <row r="78">
@@ -1899,16 +1899,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0012036984704344</v>
+        <v>0.0011901737685194</v>
       </c>
       <c r="C78" t="n">
         <v>0.000161384086657</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0010423143837774</v>
+        <v>0.0010287896818624</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0010423143837774</v>
+        <v>0.0010287896818624</v>
       </c>
     </row>
     <row r="79">
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0010180565552204</v>
+        <v>0.0010066177175213</v>
       </c>
       <c r="C79" t="n">
         <v>0.0002974417731495</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0007206147820709</v>
+        <v>0.0007091759443718</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0007206147820709</v>
+        <v>0.0007091759443718</v>
       </c>
     </row>
     <row r="80">
@@ -1937,16 +1937,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0009637412669999</v>
+        <v>0.0009529127134381</v>
       </c>
       <c r="C80" t="n">
         <v>0.0021993892491917</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.0012356479821918</v>
+        <v>-0.0012464765357536</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0012356479821918</v>
+        <v>0.0012464765357536</v>
       </c>
     </row>
     <row r="81">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0009620278725778</v>
+        <v>0.0009512185706387</v>
       </c>
       <c r="C81" t="n">
         <v>0.0010240050313402</v>
       </c>
       <c r="D81" t="n">
-        <v>-6.197715876241603e-05</v>
+        <v>-7.278646070149315e-05</v>
       </c>
       <c r="E81" t="n">
-        <v>6.197715876241603e-05</v>
+        <v>7.278646070149315e-05</v>
       </c>
     </row>
     <row r="82">
@@ -1975,16 +1975,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0009349780993537</v>
+        <v>0.0009244727274508</v>
       </c>
       <c r="C82" t="n">
         <v>0.0017363244959821</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.0008013463966283</v>
+        <v>-0.0008118517685312</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0008013463966283</v>
+        <v>0.0008118517685312</v>
       </c>
     </row>
     <row r="83">
@@ -1994,16 +1994,16 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.000803769937791</v>
+        <v>0.0007947388148944</v>
       </c>
       <c r="C83" t="n">
         <v>0.0014101943181032</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.0006064243803122</v>
+        <v>-0.0006154555032087</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0006064243803122</v>
+        <v>0.0006154555032087</v>
       </c>
     </row>
     <row r="84">
@@ -2013,16 +2013,16 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.000787555489345</v>
+        <v>0.0007787065512625001</v>
       </c>
       <c r="C84" t="n">
         <v>0.0076234627911207</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.0068359073017756</v>
+        <v>-0.0068447562398581</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0068359073017756</v>
+        <v>0.0068447562398581</v>
       </c>
     </row>
     <row r="85">
@@ -2032,16 +2032,16 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0007202439813398</v>
+        <v>0.0007121513523359</v>
       </c>
       <c r="C85" t="n">
         <v>0.0003418431354391</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0003784008459006</v>
+        <v>0.0003703082168968</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0003784008459006</v>
+        <v>0.0003703082168968</v>
       </c>
     </row>
     <row r="86">
@@ -2051,16 +2051,16 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0006415528314933</v>
+        <v>0.0006343443727125</v>
       </c>
       <c r="C86" t="n">
         <v>0.0002845466819659</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0003570061495273</v>
+        <v>0.0003497976907465</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0003570061495273</v>
+        <v>0.0003497976907465</v>
       </c>
     </row>
     <row r="87">
@@ -2070,16 +2070,16 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0005346744818135</v>
+        <v>0.0005286669033661</v>
       </c>
       <c r="C87" t="n">
         <v>0.0013206508222386</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.0007859763404251</v>
+        <v>-0.0007919839188725</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0007859763404251</v>
+        <v>0.0007919839188725</v>
       </c>
     </row>
     <row r="88">
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0005078339600264</v>
+        <v>0.0005021279604755</v>
       </c>
       <c r="C88" t="n">
         <v>0.0009308920656312</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.0004230581056048</v>
+        <v>-0.0004287641051556</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0004230581056048</v>
+        <v>0.0004287641051556</v>
       </c>
     </row>
     <row r="89">
@@ -2108,16 +2108,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0004307611771018</v>
+        <v>0.0004259211638759</v>
       </c>
       <c r="C89" t="n">
         <v>0.0005186657644225</v>
       </c>
       <c r="D89" t="n">
-        <v>-8.790458732066457e-05</v>
+        <v>-9.274460054652804e-05</v>
       </c>
       <c r="E89" t="n">
-        <v>8.790458732066457e-05</v>
+        <v>9.274460054652804e-05</v>
       </c>
     </row>
     <row r="90">
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0004289402748907</v>
+        <v>0.0004241207212403</v>
       </c>
       <c r="C90" t="n">
         <v>0.0006433899622635</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.0002144496873727</v>
+        <v>-0.0002192692410232</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0002144496873727</v>
+        <v>0.0002192692410232</v>
       </c>
     </row>
     <row r="91">
@@ -2146,16 +2146,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0004084110553374</v>
+        <v>0.0004038221670752</v>
       </c>
       <c r="C91" t="n">
         <v>0.0005898088025479</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0001813977472105</v>
+        <v>-0.0001859866354727</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0001813977472105</v>
+        <v>0.0001859866354727</v>
       </c>
     </row>
     <row r="92">
@@ -2165,16 +2165,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.0004070055839122</v>
+        <v>0.0004024324874638</v>
       </c>
       <c r="C92" t="n">
         <v>9.349765964367209e-05</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0003135079242686</v>
+        <v>0.0003089348278201</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0003135079242686</v>
+        <v>0.0003089348278201</v>
       </c>
     </row>
     <row r="93">
@@ -2184,16 +2184,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0004009375822887</v>
+        <v>0.0003964326656338</v>
       </c>
       <c r="C93" t="n">
         <v>0.0002438091277778</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0001571284545109</v>
+        <v>0.000152623537856</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0001571284545109</v>
+        <v>0.000152623537856</v>
       </c>
     </row>
     <row r="94">
@@ -2203,16 +2203,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0003812527132213</v>
+        <v>0.0003769689748705</v>
       </c>
       <c r="C94" t="n">
         <v>0.0002323696592183</v>
       </c>
       <c r="D94" t="n">
-        <v>0.000148883054003</v>
+        <v>0.0001445993156522</v>
       </c>
       <c r="E94" t="n">
-        <v>0.000148883054003</v>
+        <v>0.0001445993156522</v>
       </c>
     </row>
     <row r="95">
@@ -2222,16 +2222,16 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.0003793595202579</v>
+        <v>0.0003750970537381</v>
       </c>
       <c r="C95" t="n">
         <v>0.0066603925830795</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.0062810330628216</v>
+        <v>-0.0062852955293413</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0062810330628216</v>
+        <v>0.0062852955293413</v>
       </c>
     </row>
     <row r="96">
@@ -2241,16 +2241,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0003683782866013</v>
+        <v>0.0003642392047294</v>
       </c>
       <c r="C96" t="n">
         <v>0.0002447842918787</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0001235939947225</v>
+        <v>0.0001194549128506</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0001235939947225</v>
+        <v>0.0001194549128506</v>
       </c>
     </row>
     <row r="97">
@@ -2260,16 +2260,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0003413656558648</v>
+        <v>0.0003375300866977</v>
       </c>
       <c r="C97" t="n">
         <v>0.0003481237737581</v>
       </c>
       <c r="D97" t="n">
-        <v>-6.758117893295758e-06</v>
+        <v>-1.059368706031601e-05</v>
       </c>
       <c r="E97" t="n">
-        <v>6.758117893295758e-06</v>
+        <v>1.059368706031601e-05</v>
       </c>
     </row>
     <row r="98">
@@ -2279,16 +2279,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0003395761143626</v>
+        <v>0.0003357606524034</v>
       </c>
       <c r="C98" t="n">
         <v>0.0007195961564259</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.0003800200420633</v>
+        <v>-0.0003838355040225</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0003800200420633</v>
+        <v>0.0003838355040225</v>
       </c>
     </row>
     <row r="99">
@@ -2298,16 +2298,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0003290416288405</v>
+        <v>0.0003253445318872</v>
       </c>
       <c r="C99" t="n">
         <v>0.0001858690925899</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0001431725362505</v>
+        <v>0.0001394754392973</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0001431725362505</v>
+        <v>0.0001394754392973</v>
       </c>
     </row>
     <row r="100">
@@ -2317,168 +2317,168 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0001990113498756</v>
+        <v>0.0001967752672928</v>
       </c>
       <c r="C100" t="n">
         <v>0.0006239196240949</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.0004249082742192</v>
+        <v>-0.0004271443568021</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0004249082742192</v>
+        <v>0.0004271443568021</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Nocardiaceae</t>
+          <t>Erythrobacteraceae</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0001895070790314</v>
+        <v>0.0001883457772971</v>
       </c>
       <c r="C101" t="n">
-        <v>4.914737476060225e-05</v>
+        <v>0.0001451226010771</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0001403597042708</v>
+        <v>4.322317622003764e-05</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0001403597042708</v>
+        <v>4.322317622003764e-05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cellvibrionaceae</t>
+          <t>Nocardiaceae</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0001866387493808</v>
+        <v>0.0001873777860086</v>
       </c>
       <c r="C102" t="n">
-        <v>0.000369473403332</v>
+        <v>4.914737476060225e-05</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.0001828346539511</v>
+        <v>0.000138230411248</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0001828346539511</v>
+        <v>0.000138230411248</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Desulfuromonadaceae</t>
+          <t>Cellvibrionaceae</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0001799957926685</v>
+        <v>0.000184541684781</v>
       </c>
       <c r="C103" t="n">
-        <v>4.182558680861135e-05</v>
+        <v>0.000369473403332</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0001381702058599</v>
+        <v>-0.0001849317185509</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0001381702058599</v>
+        <v>0.0001849317185509</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Erythrobacteraceae</t>
+          <t>Desulfuromonadaceae</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.000174982134352</v>
+        <v>0.0001779733680318</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0001451226010771</v>
+        <v>4.182558680861135e-05</v>
       </c>
       <c r="D104" t="n">
-        <v>2.985953327491194e-05</v>
+        <v>0.0001361477812232</v>
       </c>
       <c r="E104" t="n">
-        <v>2.985953327491194e-05</v>
+        <v>0.0001361477812232</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Spiroplasmataceae</t>
+          <t>Deinococcaceae</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0001622077229067</v>
+        <v>0.0001681741202388</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0003295138385838</v>
+        <v>0.0006920145385135</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.000167306115677</v>
+        <v>-0.0005238404182746</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000167306115677</v>
+        <v>0.0005238404182746</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Hungateiclostridiaceae</t>
+          <t>Spiroplasmataceae</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0001560375971404</v>
+        <v>0.0001603851642224</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0006284397464561</v>
+        <v>0.0003295138385838</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.0004724021493157</v>
+        <v>-0.0001691286743614</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0004724021493157</v>
+        <v>0.0001691286743614</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Deinococcaceae</t>
+          <t>Weeksellaceae</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0001462329807578</v>
+        <v>0.0001543378917517</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0006920145385135</v>
+        <v>0.0009503366604658</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.0005457815577556</v>
+        <v>-0.000795998768714</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0005457815577556</v>
+        <v>0.000795998768714</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Weeksellaceae</t>
+          <t>Hungateiclostridiaceae</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0001425802830455</v>
+        <v>0.0001542843657118</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0009503366604658</v>
+        <v>0.0006284397464561</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.0008077563774202</v>
+        <v>-0.0004741553807442</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0008077563774202</v>
+        <v>0.0004741553807442</v>
       </c>
     </row>
     <row r="109">
@@ -2488,16 +2488,16 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0001379700438875</v>
+        <v>0.0001364198186753</v>
       </c>
       <c r="C109" t="n">
         <v>0.0011016521893749</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.0009636821454873</v>
+        <v>-0.0009652323706995</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0009636821454873</v>
+        <v>0.0009652323706995</v>
       </c>
     </row>
     <row r="110">
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0001277176303515</v>
+        <v>0.000126282600797</v>
       </c>
       <c r="C110" t="n">
         <v>0.0032786953574935</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.0031509777271419</v>
+        <v>-0.0031524127566964</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0031509777271419</v>
+        <v>0.0031524127566964</v>
       </c>
     </row>
     <row r="111">
@@ -2526,16 +2526,16 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0001036714569788</v>
+        <v>0.0001025066091476</v>
       </c>
       <c r="C111" t="n">
         <v>0.0002520870096664</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.0001484155526875</v>
+        <v>-0.0001495804005187</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0001484155526875</v>
+        <v>0.0001495804005187</v>
       </c>
     </row>
     <row r="112">
@@ -2545,16 +2545,16 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0001017767434567</v>
+        <v>0.0001006331845415</v>
       </c>
       <c r="C112" t="n">
         <v>7.961002911338978e-05</v>
       </c>
       <c r="D112" t="n">
-        <v>2.216671434337459e-05</v>
+        <v>2.102315542813005e-05</v>
       </c>
       <c r="E112" t="n">
-        <v>2.216671434337459e-05</v>
+        <v>2.102315542813005e-05</v>
       </c>
     </row>
     <row r="113">
@@ -2564,16 +2564,16 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9.912033795551148e-05</v>
+        <v>9.800662629309e-05</v>
       </c>
       <c r="C113" t="n">
         <v>9.936656976775922e-05</v>
       </c>
       <c r="D113" t="n">
-        <v>-2.462318122477394e-07</v>
+        <v>-1.359943474669211e-06</v>
       </c>
       <c r="E113" t="n">
-        <v>2.462318122477394e-07</v>
+        <v>1.359943474669211e-06</v>
       </c>
     </row>
     <row r="114">
@@ -2583,16 +2583,16 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>9.675630746175402e-05</v>
+        <v>9.566915793971184e-05</v>
       </c>
       <c r="C114" t="n">
         <v>0.0002998973879372</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.0002031410804754</v>
+        <v>-0.0002042282299975</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0002031410804754</v>
+        <v>0.0002042282299975</v>
       </c>
     </row>
     <row r="115">
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>8.213107230733767e-05</v>
+        <v>8.120825127017657e-05</v>
       </c>
       <c r="C115" t="n">
         <v>0.0004883089141366</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.0004061778418293</v>
+        <v>-0.0004071006628665</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0004061778418293</v>
+        <v>0.0004071006628665</v>
       </c>
     </row>
     <row r="116">
@@ -2621,16 +2621,16 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>7.982625259542723e-05</v>
+        <v>7.892932840896176e-05</v>
       </c>
       <c r="C116" t="n">
         <v>0.0008940053366434</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.0008141790840479</v>
+        <v>-0.0008150760082344</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0008141790840479</v>
+        <v>0.0008150760082344</v>
       </c>
     </row>
     <row r="117">
@@ -2640,16 +2640,16 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>7.873904278061289e-05</v>
+        <v>7.785433443476331e-05</v>
       </c>
       <c r="C117" t="n">
         <v>0.0003479547903006</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.00026921574752</v>
+        <v>-0.0002701004558659</v>
       </c>
       <c r="E117" t="n">
-        <v>0.00026921574752</v>
+        <v>0.0002701004558659</v>
       </c>
     </row>
     <row r="118">
@@ -2659,16 +2659,16 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>7.644537694081266e-05</v>
+        <v>7.558644012125296e-05</v>
       </c>
       <c r="C118" t="n">
         <v>5.357317514210455e-05</v>
       </c>
       <c r="D118" t="n">
-        <v>2.287220179870812e-05</v>
+        <v>2.201326497914842e-05</v>
       </c>
       <c r="E118" t="n">
-        <v>2.287220179870812e-05</v>
+        <v>2.201326497914842e-05</v>
       </c>
     </row>
     <row r="119">
@@ -2678,16 +2678,16 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7.272972509504987e-05</v>
+        <v>7.191253717263358e-05</v>
       </c>
       <c r="C119" t="n">
         <v>0.0022479373821541</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.0021752076570591</v>
+        <v>-0.0021760248449815</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0021752076570591</v>
+        <v>0.0021760248449815</v>
       </c>
     </row>
     <row r="120">
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>6.821820122246972e-05</v>
+        <v>6.745170457952061e-05</v>
       </c>
       <c r="C120" t="n">
         <v>7.185810719114092e-05</v>
       </c>
       <c r="D120" t="n">
-        <v>-3.639905968671201e-06</v>
+        <v>-4.40640261162031e-06</v>
       </c>
       <c r="E120" t="n">
-        <v>3.639905968671201e-06</v>
+        <v>4.40640261162031e-06</v>
       </c>
     </row>
     <row r="121">
@@ -2716,16 +2716,16 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>6.751281944701205e-05</v>
+        <v>6.675424844198944e-05</v>
       </c>
       <c r="C121" t="n">
         <v>0.0003648751807964</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.0002973623613493</v>
+        <v>-0.0002981209323544</v>
       </c>
       <c r="E121" t="n">
-        <v>0.0002973623613493</v>
+        <v>0.0002981209323544</v>
       </c>
     </row>
     <row r="122">
@@ -2735,16 +2735,16 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>6.580634581466262e-05</v>
+        <v>6.506694867067763e-05</v>
       </c>
       <c r="C122" t="n">
         <v>0.0003899365257775</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.0003241301799628</v>
+        <v>-0.0003248695771068</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0003241301799628</v>
+        <v>0.0003248695771068</v>
       </c>
     </row>
     <row r="123">
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4.897830926070717e-05</v>
+        <v>4.842799117912619e-05</v>
       </c>
       <c r="C123" t="n">
         <v>4.570608762940476e-05</v>
       </c>
       <c r="D123" t="n">
-        <v>3.272221631302407e-06</v>
+        <v>2.721903549721428e-06</v>
       </c>
       <c r="E123" t="n">
-        <v>3.272221631302407e-06</v>
+        <v>2.721903549721428e-06</v>
       </c>
     </row>
     <row r="124">
@@ -2773,16 +2773,16 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3.941496070631522e-05</v>
+        <v>3.897209597927797e-05</v>
       </c>
       <c r="C124" t="n">
         <v>6.652752662809849e-05</v>
       </c>
       <c r="D124" t="n">
-        <v>-2.711256592178327e-05</v>
+        <v>-2.755543064882052e-05</v>
       </c>
       <c r="E124" t="n">
-        <v>2.711256592178327e-05</v>
+        <v>2.755543064882052e-05</v>
       </c>
     </row>
     <row r="125">
@@ -2792,16 +2792,16 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3.789900067915022e-05</v>
+        <v>3.747316921084516e-05</v>
       </c>
       <c r="C125" t="n">
         <v>7.505032085404737e-05</v>
       </c>
       <c r="D125" t="n">
-        <v>-3.715132017489715e-05</v>
+        <v>-3.757715164320221e-05</v>
       </c>
       <c r="E125" t="n">
-        <v>3.715132017489715e-05</v>
+        <v>3.757715164320221e-05</v>
       </c>
     </row>
     <row r="126">
@@ -2811,16 +2811,16 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3.031469948739874e-05</v>
+        <v>2.997408488641673e-05</v>
       </c>
       <c r="C126" t="n">
         <v>0.0001580473520239</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.0001277326525365</v>
+        <v>-0.0001280732671375</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0001277326525365</v>
+        <v>0.0001280732671375</v>
       </c>
     </row>
     <row r="127">
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2.925402164234052e-05</v>
+        <v>2.892532476995467e-05</v>
       </c>
       <c r="C127" t="n">
         <v>3.222272792032821e-05</v>
       </c>
       <c r="D127" t="n">
-        <v>-2.968706277987682e-06</v>
+        <v>-3.29740315037353e-06</v>
       </c>
       <c r="E127" t="n">
-        <v>2.968706277987682e-06</v>
+        <v>3.29740315037353e-06</v>
       </c>
     </row>
     <row r="128">
@@ -2849,16 +2849,16 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2.852028728724467e-05</v>
+        <v>2.819983462109586e-05</v>
       </c>
       <c r="C128" t="n">
         <v>0.0003719752621734</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.0003434549748862</v>
+        <v>-0.0003437754275523</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0003434549748862</v>
+        <v>0.0003437754275523</v>
       </c>
     </row>
     <row r="129">
@@ -2868,16 +2868,16 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2.673833032477906e-05</v>
+        <v>2.643789964697256e-05</v>
       </c>
       <c r="C129" t="n">
         <v>0.0001756023155104</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.0001488639851856</v>
+        <v>-0.0001491644158634</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0001488639851856</v>
+        <v>0.0001491644158634</v>
       </c>
     </row>
     <row r="130">
@@ -2887,16 +2887,16 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.945428348266191e-05</v>
+        <v>1.923569602780054e-05</v>
       </c>
       <c r="C130" t="n">
         <v>1.881317979412257e-05</v>
       </c>
       <c r="D130" t="n">
-        <v>6.411036885393452e-07</v>
+        <v>4.225162336779742e-07</v>
       </c>
       <c r="E130" t="n">
-        <v>6.411036885393452e-07</v>
+        <v>4.225162336779742e-07</v>
       </c>
     </row>
     <row r="131">
@@ -2906,16 +2906,16 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.804875138811574e-05</v>
+        <v>1.784595642869871e-05</v>
       </c>
       <c r="C131" t="n">
         <v>0.0002214353740023</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.0002033866226141</v>
+        <v>-0.0002035894175736</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0002033866226141</v>
+        <v>0.0002035894175736</v>
       </c>
     </row>
     <row r="132">
@@ -2925,16 +2925,16 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.745056800704127e-05</v>
+        <v>1.725449420920935e-05</v>
       </c>
       <c r="C132" t="n">
         <v>1.514018786687024e-05</v>
       </c>
       <c r="D132" t="n">
-        <v>2.310380140171035e-06</v>
+        <v>2.114306342339112e-06</v>
       </c>
       <c r="E132" t="n">
-        <v>2.310380140171035e-06</v>
+        <v>2.114306342339112e-06</v>
       </c>
     </row>
     <row r="133">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1.574965237347e-05</v>
+        <v>1.557268998725124e-05</v>
       </c>
       <c r="C133" t="n">
         <v>2.575019144060297e-05</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.000053906713296e-05</v>
+        <v>-1.017750145335173e-05</v>
       </c>
       <c r="E133" t="n">
-        <v>1.000053906713296e-05</v>
+        <v>1.017750145335173e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2967,7 +2967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>0.9915738489565016</t>
+          <t>0.9924699956344532</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.893473931289033e-117</v>
+        <v>1.99306702102683e-120</v>
       </c>
     </row>
     <row r="4">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>0.9915738489565016</t>
+          <t>0.9924699956344532</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>0.9849468218384722</t>
+          <t>0.9861869517661188</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>0.9630498230621352</t>
+          <t>0.963464181762324</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK139"/>
+  <dimension ref="A1:CL139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3540,6 +3540,11 @@
           <t>SRR26147516</t>
         </is>
       </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>SRR26147254</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3811,6 +3816,9 @@
       <c r="CK2" t="n">
         <v>0.0106211059110483</v>
       </c>
+      <c r="CL2" t="n">
+        <v>0.0011544469170116</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4082,6 +4090,9 @@
       <c r="CK3" t="n">
         <v>0.0102958322582355</v>
       </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4353,6 +4364,9 @@
       <c r="CK4" t="n">
         <v>0.0305631802580232</v>
       </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4624,6 +4638,9 @@
       <c r="CK5" t="n">
         <v>0.003418975315417</v>
       </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4895,6 +4912,9 @@
       <c r="CK6" t="n">
         <v>0.0017181005291655</v>
       </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5166,6 +5186,9 @@
       <c r="CK7" t="n">
         <v>0</v>
       </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5437,6 +5460,9 @@
       <c r="CK8" t="n">
         <v>0.0036553340420854</v>
       </c>
+      <c r="CL8" t="n">
+        <v>0.0168969048831352</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5708,6 +5734,9 @@
       <c r="CK9" t="n">
         <v>0.0039563398140837</v>
       </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5979,6 +6008,9 @@
       <c r="CK10" t="n">
         <v>0.0036790799054378</v>
       </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6250,6 +6282,9 @@
       <c r="CK11" t="n">
         <v>0.0024430175849466</v>
       </c>
+      <c r="CL11" t="n">
+        <v>0.012384066927206</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6521,6 +6556,9 @@
       <c r="CK12" t="n">
         <v>0.0009172594222375</v>
       </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6792,6 +6830,9 @@
       <c r="CK13" t="n">
         <v>0.0566168196193248</v>
       </c>
+      <c r="CL13" t="n">
+        <v>0.0026237429932081</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7063,6 +7104,9 @@
       <c r="CK14" t="n">
         <v>0</v>
       </c>
+      <c r="CL14" t="n">
+        <v>0.0120692238963189</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7334,6 +7378,9 @@
       <c r="CK15" t="n">
         <v>0.0103822013324812</v>
       </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7605,6 +7652,9 @@
       <c r="CK16" t="n">
         <v>0</v>
       </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7876,6 +7926,9 @@
       <c r="CK17" t="n">
         <v>0</v>
       </c>
+      <c r="CL17" t="n">
+        <v>0.0023088938340232</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8147,6 +8200,9 @@
       <c r="CK18" t="n">
         <v>0.0054817921374861</v>
       </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8418,6 +8474,9 @@
       <c r="CK19" t="n">
         <v>0.0388000282504829</v>
       </c>
+      <c r="CL19" t="n">
+        <v>0.0027286927129365</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8689,6 +8748,9 @@
       <c r="CK20" t="n">
         <v>0.001942251291313</v>
       </c>
+      <c r="CL20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8960,6 +9022,9 @@
       <c r="CK21" t="n">
         <v>0</v>
       </c>
+      <c r="CL21" t="n">
+        <v>0.009523526377485899</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9231,6 +9296,9 @@
       <c r="CK22" t="n">
         <v>0.0013186233470463</v>
       </c>
+      <c r="CL22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9502,6 +9570,9 @@
       <c r="CK23" t="n">
         <v>0.0012612317070807</v>
       </c>
+      <c r="CL23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9773,6 +9844,9 @@
       <c r="CK24" t="n">
         <v>0.001719854141079</v>
       </c>
+      <c r="CL24" t="n">
+        <v>0.0022039441142948</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10044,6 +10118,9 @@
       <c r="CK25" t="n">
         <v>0</v>
       </c>
+      <c r="CL25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10315,6 +10392,9 @@
       <c r="CK26" t="n">
         <v>0</v>
       </c>
+      <c r="CL26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10586,6 +10666,9 @@
       <c r="CK27" t="n">
         <v>0.0239063480251404</v>
       </c>
+      <c r="CL27" t="n">
+        <v>0.0449184800437325</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10857,6 +10940,9 @@
       <c r="CK28" t="n">
         <v>0</v>
       </c>
+      <c r="CL28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11128,6 +11214,9 @@
       <c r="CK29" t="n">
         <v>0.09026056730232521</v>
       </c>
+      <c r="CL29" t="n">
+        <v>0.0022039441142948</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11399,6 +11488,9 @@
       <c r="CK30" t="n">
         <v>0.0009172534891021</v>
       </c>
+      <c r="CL30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11670,6 +11762,9 @@
       <c r="CK31" t="n">
         <v>0.0056630804806459</v>
       </c>
+      <c r="CL31" t="n">
+        <v>0.0379999292028044</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11941,6 +12036,9 @@
       <c r="CK32" t="n">
         <v>0.0121723866921202</v>
       </c>
+      <c r="CL32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12212,6 +12310,9 @@
       <c r="CK33" t="n">
         <v>0.0047597774855487</v>
       </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12483,6 +12584,9 @@
       <c r="CK34" t="n">
         <v>0.0007452732805323</v>
       </c>
+      <c r="CL34" t="n">
+        <v>0.0213047931048941</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12754,6 +12858,9 @@
       <c r="CK35" t="n">
         <v>0</v>
       </c>
+      <c r="CL35" t="n">
+        <v>0.0020989943945665</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -13025,6 +13132,9 @@
       <c r="CK36" t="n">
         <v>0</v>
       </c>
+      <c r="CL36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13296,6 +13406,9 @@
       <c r="CK37" t="n">
         <v>0</v>
       </c>
+      <c r="CL37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13567,6 +13680,9 @@
       <c r="CK38" t="n">
         <v>0</v>
       </c>
+      <c r="CL38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13838,6 +13954,9 @@
       <c r="CK39" t="n">
         <v>0.0019316222552143</v>
       </c>
+      <c r="CL39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14109,6 +14228,9 @@
       <c r="CK40" t="n">
         <v>0</v>
       </c>
+      <c r="CL40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14380,6 +14502,9 @@
       <c r="CK41" t="n">
         <v>0</v>
       </c>
+      <c r="CL41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14651,6 +14776,9 @@
       <c r="CK42" t="n">
         <v>0</v>
       </c>
+      <c r="CL42" t="n">
+        <v>0.0013643463564682</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14922,6 +15050,9 @@
       <c r="CK43" t="n">
         <v>0</v>
       </c>
+      <c r="CL43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15193,6 +15324,9 @@
       <c r="CK44" t="n">
         <v>0.0009172594229837</v>
       </c>
+      <c r="CL44" t="n">
+        <v>0.0035682904707631</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15464,6 +15598,9 @@
       <c r="CK45" t="n">
         <v>0.001777190132031</v>
       </c>
+      <c r="CL45" t="n">
+        <v>0.0186810501116421</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15735,6 +15872,9 @@
       <c r="CK46" t="n">
         <v>0.00667249395929</v>
       </c>
+      <c r="CL46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16006,6 +16146,9 @@
       <c r="CK47" t="n">
         <v>0</v>
       </c>
+      <c r="CL47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16277,6 +16420,9 @@
       <c r="CK48" t="n">
         <v>0.1451105836774522</v>
       </c>
+      <c r="CL48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16548,6 +16694,9 @@
       <c r="CK49" t="n">
         <v>0</v>
       </c>
+      <c r="CL49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16819,6 +16968,9 @@
       <c r="CK50" t="n">
         <v>0.0210421338472547</v>
       </c>
+      <c r="CL50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17090,6 +17242,9 @@
       <c r="CK51" t="n">
         <v>0.0143974048619047</v>
       </c>
+      <c r="CL51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17361,6 +17516,9 @@
       <c r="CK52" t="n">
         <v>0.0032561009852361</v>
       </c>
+      <c r="CL52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17632,6 +17790,9 @@
       <c r="CK53" t="n">
         <v>0</v>
       </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17903,6 +18064,9 @@
       <c r="CK54" t="n">
         <v>0</v>
       </c>
+      <c r="CL54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -18174,6 +18338,9 @@
       <c r="CK55" t="n">
         <v>0</v>
       </c>
+      <c r="CL55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -18445,6 +18612,9 @@
       <c r="CK56" t="n">
         <v>0.0018358947157505</v>
       </c>
+      <c r="CL56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -18716,6 +18886,9 @@
       <c r="CK57" t="n">
         <v>0.0300378008359049</v>
       </c>
+      <c r="CL57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18987,6 +19160,9 @@
       <c r="CK58" t="n">
         <v>0.0040692820183038</v>
       </c>
+      <c r="CL58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19258,6 +19434,9 @@
       <c r="CK59" t="n">
         <v>0.0052771731690488</v>
       </c>
+      <c r="CL59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -19529,6 +19708,9 @@
       <c r="CK60" t="n">
         <v>0</v>
       </c>
+      <c r="CL60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19800,6 +19982,9 @@
       <c r="CK61" t="n">
         <v>0.009667111637121801</v>
       </c>
+      <c r="CL61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -20071,6 +20256,9 @@
       <c r="CK62" t="n">
         <v>0.0072899470229071</v>
       </c>
+      <c r="CL62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20342,6 +20530,9 @@
       <c r="CK63" t="n">
         <v>0.0006306360948111</v>
       </c>
+      <c r="CL63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20613,6 +20804,9 @@
       <c r="CK64" t="n">
         <v>0.0023355713611462</v>
       </c>
+      <c r="CL64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -20884,6 +21078,9 @@
       <c r="CK65" t="n">
         <v>0</v>
       </c>
+      <c r="CL65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -21155,6 +21352,9 @@
       <c r="CK66" t="n">
         <v>0.0025661312959683</v>
       </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -21426,6 +21626,9 @@
       <c r="CK67" t="n">
         <v>0</v>
       </c>
+      <c r="CL67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -21697,6 +21900,9 @@
       <c r="CK68" t="n">
         <v>0</v>
       </c>
+      <c r="CL68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21968,6 +22174,9 @@
       <c r="CK69" t="n">
         <v>0.006039697120851</v>
       </c>
+      <c r="CL69" t="n">
+        <v>0.004512837948318</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22239,6 +22448,9 @@
       <c r="CK70" t="n">
         <v>0.0059395152528906</v>
       </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -22510,6 +22722,9 @@
       <c r="CK71" t="n">
         <v>0</v>
       </c>
+      <c r="CL71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -22781,6 +22996,9 @@
       <c r="CK72" t="n">
         <v>0.0017777133721688</v>
       </c>
+      <c r="CL72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -23052,6 +23270,9 @@
       <c r="CK73" t="n">
         <v>0.0038409062743441</v>
       </c>
+      <c r="CL73" t="n">
+        <v>0.0053524357061447</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -23323,6 +23544,9 @@
       <c r="CK74" t="n">
         <v>0.0052571814776311</v>
       </c>
+      <c r="CL74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -23594,6 +23818,9 @@
       <c r="CK75" t="n">
         <v>0</v>
       </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -23865,6 +24092,9 @@
       <c r="CK76" t="n">
         <v>0</v>
       </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -24136,6 +24366,9 @@
       <c r="CK77" t="n">
         <v>0</v>
       </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -24407,6 +24640,9 @@
       <c r="CK78" t="n">
         <v>0</v>
       </c>
+      <c r="CL78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24678,6 +24914,9 @@
       <c r="CK79" t="n">
         <v>0.0028803332046702</v>
       </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24949,6 +25188,9 @@
       <c r="CK80" t="n">
         <v>0.0135993112427801</v>
       </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -25220,6 +25462,9 @@
       <c r="CK81" t="n">
         <v>0.0013873099217854</v>
       </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -25491,6 +25736,9 @@
       <c r="CK82" t="n">
         <v>0.0051851409893307</v>
       </c>
+      <c r="CL82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -25762,6 +26010,9 @@
       <c r="CK83" t="n">
         <v>0</v>
       </c>
+      <c r="CL83" t="n">
+        <v>0.0026237429931952</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -26033,6 +26284,9 @@
       <c r="CK84" t="n">
         <v>0.0007452732811743</v>
       </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -26304,6 +26558,9 @@
       <c r="CK85" t="n">
         <v>0</v>
       </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -26575,6 +26832,9 @@
       <c r="CK86" t="n">
         <v>0.0033819649129397</v>
       </c>
+      <c r="CL86" t="n">
+        <v>0.6487942249699619</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -26846,6 +27106,9 @@
       <c r="CK87" t="n">
         <v>0.0050449355234111</v>
       </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -27117,6 +27380,9 @@
       <c r="CK88" t="n">
         <v>0.0040659413593207</v>
       </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27388,6 +27654,9 @@
       <c r="CK89" t="n">
         <v>0.0036110359884697</v>
       </c>
+      <c r="CL89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27659,6 +27928,9 @@
       <c r="CK90" t="n">
         <v>0</v>
       </c>
+      <c r="CL90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27930,6 +28202,9 @@
       <c r="CK91" t="n">
         <v>0</v>
       </c>
+      <c r="CL91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -28201,6 +28476,9 @@
       <c r="CK92" t="n">
         <v>0.0023504772713964</v>
       </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28472,6 +28750,9 @@
       <c r="CK93" t="n">
         <v>0.0023825286902262</v>
       </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -28743,6 +29024,9 @@
       <c r="CK94" t="n">
         <v>0.0049331622247018</v>
       </c>
+      <c r="CL94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -29014,6 +29298,9 @@
       <c r="CK95" t="n">
         <v>0.0013089070972593</v>
       </c>
+      <c r="CL95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -29285,6 +29572,9 @@
       <c r="CK96" t="n">
         <v>0.0068681762368086</v>
       </c>
+      <c r="CL96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -29556,6 +29846,9 @@
       <c r="CK97" t="n">
         <v>0.0384497031522996</v>
       </c>
+      <c r="CL97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -29827,6 +30120,9 @@
       <c r="CK98" t="n">
         <v>0</v>
       </c>
+      <c r="CL98" t="n">
+        <v>0.0343212896456172</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -30098,6 +30394,9 @@
       <c r="CK99" t="n">
         <v>0</v>
       </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -30369,6 +30668,9 @@
       <c r="CK100" t="n">
         <v>0.0247749986502758</v>
       </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -30640,6 +30942,9 @@
       <c r="CK101" t="n">
         <v>0</v>
       </c>
+      <c r="CL101" t="n">
+        <v>0.0216196422640354</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -30911,6 +31216,9 @@
       <c r="CK102" t="n">
         <v>0.0021834351239266</v>
       </c>
+      <c r="CL102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -31182,6 +31490,9 @@
       <c r="CK103" t="n">
         <v>0</v>
       </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -31453,6 +31764,9 @@
       <c r="CK104" t="n">
         <v>0</v>
       </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -31724,6 +32038,9 @@
       <c r="CK105" t="n">
         <v>0.0129827210641262</v>
       </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -31995,6 +32312,9 @@
       <c r="CK106" t="n">
         <v>0.0012039029927788</v>
       </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -32266,6 +32586,9 @@
       <c r="CK107" t="n">
         <v>0.0037589112250639</v>
       </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -32537,6 +32860,9 @@
       <c r="CK108" t="n">
         <v>0</v>
       </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -32808,6 +33134,9 @@
       <c r="CK109" t="n">
         <v>0</v>
       </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -33079,6 +33408,9 @@
       <c r="CK110" t="n">
         <v>0.0147050773615061</v>
       </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -33350,6 +33682,9 @@
       <c r="CK111" t="n">
         <v>0.0239420093093519</v>
       </c>
+      <c r="CL111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -33621,6 +33956,9 @@
       <c r="CK112" t="n">
         <v>0</v>
       </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -33892,6 +34230,9 @@
       <c r="CK113" t="n">
         <v>0</v>
       </c>
+      <c r="CL113" t="n">
+        <v>0.0171068043165828</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -34163,6 +34504,9 @@
       <c r="CK114" t="n">
         <v>0.0061921039908058</v>
       </c>
+      <c r="CL114" t="n">
+        <v>0.0023088938340232</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -34434,6 +34778,9 @@
       <c r="CK115" t="n">
         <v>0</v>
       </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -34705,6 +35052,9 @@
       <c r="CK116" t="n">
         <v>0.001454980865681</v>
       </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -34976,6 +35326,9 @@
       <c r="CK117" t="n">
         <v>0</v>
       </c>
+      <c r="CL117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -35247,6 +35600,9 @@
       <c r="CK118" t="n">
         <v>0.0114763439252843</v>
       </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -35518,6 +35874,9 @@
       <c r="CK119" t="n">
         <v>0.004673684676414</v>
       </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -35789,6 +36148,9 @@
       <c r="CK120" t="n">
         <v>0.0052678282124746</v>
       </c>
+      <c r="CL120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -36060,6 +36422,9 @@
       <c r="CK121" t="n">
         <v>0.002003386039483</v>
       </c>
+      <c r="CL121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -36331,6 +36696,9 @@
       <c r="CK122" t="n">
         <v>0.0019606298007286</v>
       </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -36602,6 +36970,9 @@
       <c r="CK123" t="n">
         <v>0.0062488298192224</v>
       </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -36873,6 +37244,9 @@
       <c r="CK124" t="n">
         <v>0.0149294877350397</v>
       </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -37144,6 +37518,9 @@
       <c r="CK125" t="n">
         <v>0</v>
       </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -37415,6 +37792,9 @@
       <c r="CK126" t="n">
         <v>0</v>
       </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -37686,6 +38066,9 @@
       <c r="CK127" t="n">
         <v>0.0008833723952062</v>
       </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -37957,6 +38340,9 @@
       <c r="CK128" t="n">
         <v>0.0031937043886557</v>
       </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -38228,6 +38614,9 @@
       <c r="CK129" t="n">
         <v>0.0012275322099746</v>
       </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -38499,6 +38888,9 @@
       <c r="CK130" t="n">
         <v>0.0008025834849984</v>
       </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -38770,6 +39162,9 @@
       <c r="CK131" t="n">
         <v>0.0088667976694153</v>
       </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -39041,6 +39436,9 @@
       <c r="CK132" t="n">
         <v>0.0106621296520661</v>
       </c>
+      <c r="CL132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -39312,6 +39710,9 @@
       <c r="CK133" t="n">
         <v>0.1054070093992131</v>
       </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -39583,6 +39984,9 @@
       <c r="CK134" t="n">
         <v>0.0007180784201084</v>
       </c>
+      <c r="CL134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -39854,6 +40258,9 @@
       <c r="CK135" t="n">
         <v>0</v>
       </c>
+      <c r="CL135" t="n">
+        <v>0.0011890074578985</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -40125,6 +40532,9 @@
       <c r="CK136" t="n">
         <v>0.0131160776654277</v>
       </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -40396,6 +40806,9 @@
       <c r="CK137" t="n">
         <v>0.0108921433544562</v>
       </c>
+      <c r="CL137" t="n">
+        <v>0.06813785040943619</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -40667,6 +41080,9 @@
       <c r="CK138" t="n">
         <v>0</v>
       </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -40937,6 +41353,9 @@
       </c>
       <c r="CK139" t="n">
         <v>0.0013929750591337</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
